--- a/data/trans_dic/P15D$consultar-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P15D$consultar-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya consecuencia del último accidente fue, al menos, consultar con un profesional sanitario (fuera de un hospital)</t>
+          <t>Población cuya consecuencia del último accidente fue, al menos, consultar con un profesional sanitario (fuera de un hospital) (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 22,45</t>
+          <t>2,56; 20,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 14,25</t>
+          <t>1,56; 14,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,95</t>
+          <t>0,0; 12,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,45</t>
+          <t>0,0; 57,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,56; 66,57</t>
+          <t>10,12; 66,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,08; 25,14</t>
+          <t>3,06; 25,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,65</t>
+          <t>0,0; 22,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,46</t>
+          <t>0,0; 47,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,58; 27,66</t>
+          <t>6,62; 29,02</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,19; 13,74</t>
+          <t>3,14; 13,88</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,41</t>
+          <t>0,0; 10,62</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,51; 38,71</t>
+          <t>3,6; 36,98</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,88; 25,95</t>
+          <t>2,83; 25,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,31; 17,16</t>
+          <t>3,37; 16,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,4; 24,37</t>
+          <t>5,4; 22,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,67</t>
+          <t>0,0; 32,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,6; 23,88</t>
+          <t>2,61; 23,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,77</t>
+          <t>0,0; 25,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,71; 69,9</t>
+          <t>19,64; 69,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 17,02</t>
+          <t>1,91; 17,81</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,73; 16,06</t>
+          <t>4,9; 16,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,04; 19,61</t>
+          <t>6,15; 20,27</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,41; 35,86</t>
+          <t>7,49; 38,22</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,27; 60,75</t>
+          <t>6,8; 58,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,22; 24,01</t>
+          <t>4,98; 23,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,83; 32,61</t>
+          <t>5,52; 31,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,07</t>
+          <t>0,0; 53,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,97; 23,54</t>
+          <t>2,81; 23,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,32</t>
+          <t>3,44; 27,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,05; 33,54</t>
+          <t>8,25; 34,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,59; 44,65</t>
+          <t>9,94; 47,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,72; 19,15</t>
+          <t>5,71; 19,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,25; 24,7</t>
+          <t>6,15; 24,67</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,62; 15,26</t>
+          <t>3,56; 14,94</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,86; 39,73</t>
+          <t>4,81; 42,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,92; 30,99</t>
+          <t>5,84; 31,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,66; 32,15</t>
+          <t>3,61; 30,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,12; 19,08</t>
+          <t>2,71; 22,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,47</t>
+          <t>0,0; 24,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,96; 33,81</t>
+          <t>1,82; 31,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,93; 24,95</t>
+          <t>4,71; 24,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,22; 25,65</t>
+          <t>0,0; 27,39</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,01; 22,17</t>
+          <t>5,24; 23,2</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,83; 26,49</t>
+          <t>6,47; 26,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,37; 18,06</t>
+          <t>4,68; 17,57</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,45</t>
+          <t>0,0; 47,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,48</t>
+          <t>0,0; 38,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,02; 29,29</t>
+          <t>3,48; 28,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,0</t>
+          <t>0,0; 50,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,13</t>
+          <t>0,0; 17,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,36; 23,12</t>
+          <t>5,16; 22,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,03</t>
+          <t>0,0; 32,49</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,04</t>
+          <t>0,0; 12,55</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,22</t>
+          <t>0,0; 12,82</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,79; 20,31</t>
+          <t>6,49; 20,14</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,55</t>
+          <t>0,0; 31,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,56; 55,93</t>
+          <t>7,33; 56,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,09</t>
+          <t>0,0; 30,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,52</t>
+          <t>0,0; 45,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,48; 42,99</t>
+          <t>11,45; 42,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,33; 37,14</t>
+          <t>6,93; 37,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,86; 22,46</t>
+          <t>4,24; 20,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,78</t>
+          <t>0,0; 42,9</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,87; 30,67</t>
+          <t>6,9; 28,8</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11,43; 35,48</t>
+          <t>11,67; 35,51</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,82; 19,0</t>
+          <t>4,99; 18,67</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,75</t>
+          <t>0,0; 67,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,02; 49,51</t>
+          <t>10,28; 50,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,93; 29,76</t>
+          <t>6,22; 28,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,72; 35,67</t>
+          <t>4,74; 35,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,89</t>
+          <t>0,0; 11,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,96; 26,57</t>
+          <t>3,04; 27,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17,09; 33,95</t>
+          <t>17,13; 33,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,83; 33,3</t>
+          <t>4,1; 34,86</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,41</t>
+          <t>0,0; 7,26</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,97; 27,97</t>
+          <t>7,38; 28,86</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15,75; 29,4</t>
+          <t>16,19; 29,89</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,3; 20,55</t>
+          <t>8,14; 20,21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,43; 11,82</t>
+          <t>5,15; 11,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,44; 18,12</t>
+          <t>8,8; 18,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,08; 14,18</t>
+          <t>5,2; 14,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,93; 22,56</t>
+          <t>7,27; 21,86</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,48; 12,97</t>
+          <t>5,32; 12,35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,21; 15,18</t>
+          <t>6,63; 15,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,27; 23,35</t>
+          <t>14,49; 23,91</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,19; 18,71</t>
+          <t>8,86; 18,51</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6,28; 11,4</t>
+          <t>6,03; 11,18</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8,54; 15,16</t>
+          <t>8,61; 14,69</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,86; 17,44</t>
+          <t>11,09; 17,28</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuya consecuencia del último accidente fue, al menos, consultar con un profesional sanitario (fuera de un hospital)</t>
+          <t>Población cuya consecuencia del último accidente fue, al menos, consultar con un profesional sanitario (fuera de un hospital) (tasa de respuesta: 89,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>891; 7568</t>
+          <t>863; 7025</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>934; 8496</t>
+          <t>933; 8550</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5258</t>
+          <t>0; 5293</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 10994</t>
+          <t>0; 11019</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1012; 7048</t>
+          <t>1071; 7023</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>946; 7708</t>
+          <t>939; 7841</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3954</t>
+          <t>0; 4144</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 9458</t>
+          <t>0; 9549</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2913; 12255</t>
+          <t>2934; 12856</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2882; 12406</t>
+          <t>2832; 12532</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 7101</t>
+          <t>0; 6609</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1370; 15121</t>
+          <t>1405; 14447</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1005; 9066</t>
+          <t>990; 8877</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2723; 14126</t>
+          <t>2771; 13646</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2747; 12393</t>
+          <t>2747; 11600</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 9180</t>
+          <t>0; 8984</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1955</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>988; 9082</t>
+          <t>991; 8945</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5844</t>
+          <t>0; 5732</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2952; 10467</t>
+          <t>2941; 10386</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1001; 9104</t>
+          <t>1024; 9529</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5698; 19326</t>
+          <t>5895; 19891</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3710; 14420</t>
+          <t>4520; 14904</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3554; 15148</t>
+          <t>3165; 16142</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1534; 9070</t>
+          <t>1016; 8781</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2785; 12822</t>
+          <t>2662; 12533</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2809; 11694</t>
+          <t>1981; 11249</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2018</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 7790</t>
+          <t>0; 7142</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>872; 6919</t>
+          <t>825; 6878</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6843</t>
+          <t>862; 6911</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2538; 9402</t>
+          <t>2313; 9585</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2719; 12658</t>
+          <t>2817; 13522</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4740; 15859</t>
+          <t>4728; 16418</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3807; 15046</t>
+          <t>3745; 15026</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2357; 9928</t>
+          <t>2317; 9716</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>950; 7762</t>
+          <t>940; 8391</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2142; 11206</t>
+          <t>2112; 11228</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1055; 9268</t>
+          <t>1040; 8890</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1075; 9672</t>
+          <t>1373; 11152</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1811</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 9262</t>
+          <t>0; 8543</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>970; 8277</t>
+          <t>447; 7699</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1742; 7333</t>
+          <t>1385; 7304</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>939; 7490</t>
+          <t>0; 8000</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3563; 15770</t>
+          <t>3730; 16502</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3107; 14123</t>
+          <t>3449; 14301</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4303; 14465</t>
+          <t>3745; 14069</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4259</t>
+          <t>0; 4441</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 1874</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5242</t>
+          <t>0; 5319</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1162; 8476</t>
+          <t>1008; 8229</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4935</t>
+          <t>0; 4995</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 6735</t>
+          <t>0; 7427</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 2142</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1897; 8181</t>
+          <t>1826; 7898</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 6163</t>
+          <t>0; 6252</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 6586</t>
+          <t>0; 6861</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 5421</t>
+          <t>0; 5685</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4367; 13063</t>
+          <t>4174; 12956</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1423</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5458</t>
+          <t>0; 5438</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>827; 6114</t>
+          <t>802; 6208</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 4900</t>
+          <t>0; 5042</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4969</t>
+          <t>0; 4120</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2908; 10890</t>
+          <t>2901; 10848</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2733; 10882</t>
+          <t>2031; 11013</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1603; 7399</t>
+          <t>1396; 6661</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 5063</t>
+          <t>0; 5906</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2928; 13073</t>
+          <t>2941; 12278</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4598; 14273</t>
+          <t>4695; 14285</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2374; 9354</t>
+          <t>2456; 9192</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3723</t>
+          <t>0; 4013</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 1904</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1522; 7518</t>
+          <t>1561; 7601</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1230; 6171</t>
+          <t>1291; 5907</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1067; 8061</t>
+          <t>1071; 8054</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 5359</t>
+          <t>0; 6373</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1188; 10662</t>
+          <t>1218; 11111</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>9051; 17976</t>
+          <t>9068; 17570</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1093; 9502</t>
+          <t>1171; 9948</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 4882</t>
+          <t>0; 5534</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4408; 15470</t>
+          <t>4081; 15966</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>11607; 21666</t>
+          <t>11930; 22023</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>10210; 25289</t>
+          <t>10013; 24879</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>15411; 33541</t>
+          <t>14609; 33785</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>16848; 36178</t>
+          <t>17558; 36131</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>10158; 28360</t>
+          <t>10397; 29251</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>6496; 21166</t>
+          <t>6823; 20507</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>13931; 32991</t>
+          <t>13536; 31420</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11817; 28885</t>
+          <t>12618; 29936</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>30477; 49877</t>
+          <t>30958; 51066</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>19934; 40590</t>
+          <t>19210; 40138</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>33805; 61371</t>
+          <t>32422; 60169</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>33298; 59107</t>
+          <t>33563; 57282</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>44914; 72141</t>
+          <t>45885; 71479</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15D$consultar-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P15D$consultar-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 20,84</t>
+          <t>2,64; 20,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,56; 14,34</t>
+          <t>1,58; 14,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,04</t>
+          <t>0,0; 11,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,58</t>
+          <t>0,0; 54,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,12; 66,34</t>
+          <t>9,94; 65,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,06; 25,57</t>
+          <t>3,09; 26,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,69</t>
+          <t>0,0; 25,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,92</t>
+          <t>0,0; 41,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,62; 29,02</t>
+          <t>6,52; 27,18</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,14; 13,88</t>
+          <t>3,21; 14,77</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,62</t>
+          <t>0,0; 11,71</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,6; 36,98</t>
+          <t>3,29; 36,36</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>16,87%</t>
         </is>
       </c>
     </row>
@@ -857,22 +857,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 25,41</t>
+          <t>2,83; 25,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,37; 16,58</t>
+          <t>3,38; 17,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,4; 22,81</t>
+          <t>5,46; 24,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,95</t>
+          <t>0,0; 28,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,37 +882,37 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,61; 23,52</t>
+          <t>2,96; 24,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,27</t>
+          <t>0,0; 25,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,64; 69,36</t>
+          <t>18,7; 68,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 17,81</t>
+          <t>1,83; 16,29</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,9; 16,53</t>
+          <t>4,64; 15,64</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,15; 20,27</t>
+          <t>5,13; 20,3</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,49; 38,22</t>
+          <t>8,19; 34,56</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -997,17 +997,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,8; 58,81</t>
+          <t>10,32; 58,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,98; 23,47</t>
+          <t>4,81; 23,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,52; 31,37</t>
+          <t>5,79; 29,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1017,42 +1017,42 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,23</t>
+          <t>0,0; 57,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,81; 23,4</t>
+          <t>3,04; 23,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,44; 27,59</t>
+          <t>3,47; 30,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,25; 34,19</t>
+          <t>9,4; 34,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,94; 47,7</t>
+          <t>10,69; 46,07</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,71; 19,83</t>
+          <t>5,38; 19,99</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,15; 24,67</t>
+          <t>7,3; 24,32</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 14,94</t>
+          <t>3,87; 16,53</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,81; 42,94</t>
+          <t>1,97; 39,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,84; 31,05</t>
+          <t>5,87; 31,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,61; 30,83</t>
+          <t>3,74; 31,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,71; 22,0</t>
+          <t>2,09; 19,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,37 +1162,37 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,42</t>
+          <t>0,0; 27,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 31,44</t>
+          <t>3,96; 32,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,71; 24,85</t>
+          <t>4,09; 22,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,39</t>
+          <t>3,27; 27,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,24; 23,2</t>
+          <t>5,4; 22,2</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,47; 26,82</t>
+          <t>5,7; 25,81</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,68; 17,57</t>
+          <t>4,58; 17,36</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,4</t>
+          <t>0,0; 44,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1287,22 +1287,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,02</t>
+          <t>0,0; 30,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,48; 28,44</t>
+          <t>4,98; 29,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,61</t>
+          <t>0,0; 43,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,79</t>
+          <t>0,0; 18,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1312,27 +1312,27 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,16; 22,32</t>
+          <t>5,32; 22,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,49</t>
+          <t>0,0; 30,21</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,55</t>
+          <t>0,0; 13,06</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,82</t>
+          <t>0,0; 14,15</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,49; 20,14</t>
+          <t>6,83; 21,14</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -1422,57 +1422,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,44</t>
+          <t>0,0; 24,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,33; 56,78</t>
+          <t>0,0; 55,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,96</t>
+          <t>0,0; 27,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,21</t>
+          <t>0,0; 54,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,45; 42,82</t>
+          <t>11,52; 42,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,93; 37,59</t>
+          <t>6,82; 37,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,24; 20,22</t>
+          <t>4,43; 20,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,9</t>
+          <t>0,0; 30,46</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,9; 28,8</t>
+          <t>6,8; 28,69</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11,67; 35,51</t>
+          <t>11,57; 37,19</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,99; 18,67</t>
+          <t>4,43; 16,97</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>23,13%</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,64</t>
+          <t>0,0; 67,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1567,52 +1567,52 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,28; 50,05</t>
+          <t>10,32; 49,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,22; 28,49</t>
+          <t>7,55; 35,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,74; 35,64</t>
+          <t>4,68; 36,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,76</t>
+          <t>0,0; 9,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,04; 27,69</t>
+          <t>3,17; 27,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17,13; 33,18</t>
+          <t>17,84; 35,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,1; 34,86</t>
+          <t>4,15; 33,5</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,26</t>
+          <t>0,0; 5,84</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,38; 28,86</t>
+          <t>7,28; 27,76</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16,19; 29,89</t>
+          <t>16,97; 31,17</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,14; 20,21</t>
+          <t>7,87; 20,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,15; 11,91</t>
+          <t>5,12; 11,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,8; 18,1</t>
+          <t>8,81; 17,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,2; 14,62</t>
+          <t>5,09; 13,76</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,27; 21,86</t>
+          <t>6,55; 21,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,32; 12,35</t>
+          <t>5,49; 12,51</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,63; 15,73</t>
+          <t>6,09; 15,42</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>14,49; 23,91</t>
+          <t>14,24; 23,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,86; 18,51</t>
+          <t>8,81; 17,68</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6,03; 11,18</t>
+          <t>6,21; 11,2</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8,61; 14,69</t>
+          <t>8,6; 15,22</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,09; 17,28</t>
+          <t>10,64; 16,99</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2578</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5727</t>
+          <t>5924</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>863; 7025</t>
+          <t>890; 6744</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>933; 8550</t>
+          <t>943; 8485</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5293</t>
+          <t>0; 5264</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 11019</t>
+          <t>0; 11287</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1071; 7023</t>
+          <t>1052; 6977</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>939; 7841</t>
+          <t>948; 8013</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4144</t>
+          <t>0; 4715</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 9549</t>
+          <t>0; 9426</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2934; 12856</t>
+          <t>2888; 12040</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2832; 12532</t>
+          <t>2898; 13339</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 6609</t>
+          <t>0; 7289</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1405; 14447</t>
+          <t>1426; 15741</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6292</t>
+          <t>6275</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8275</t>
+          <t>8188</t>
         </is>
       </c>
     </row>
@@ -2276,22 +2276,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>990; 8877</t>
+          <t>990; 9073</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2771; 13646</t>
+          <t>2784; 14413</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2747; 11600</t>
+          <t>2775; 12311</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 8984</t>
+          <t>0; 9620</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2301,37 +2301,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>991; 8945</t>
+          <t>1126; 9164</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5732</t>
+          <t>0; 5855</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2941; 10386</t>
+          <t>2867; 10449</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1024; 9529</t>
+          <t>977; 8711</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5895; 19891</t>
+          <t>5585; 18822</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4520; 14904</t>
+          <t>3769; 14931</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3165; 16142</t>
+          <t>3973; 16771</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5908</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5908</t>
         </is>
       </c>
     </row>
@@ -2484,17 +2484,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1016; 8781</t>
+          <t>1541; 8689</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2662; 12533</t>
+          <t>2570; 12457</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1981; 11249</t>
+          <t>2076; 10477</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -2504,42 +2504,42 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 7142</t>
+          <t>0; 7696</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>825; 6878</t>
+          <t>893; 6861</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>862; 6911</t>
+          <t>870; 7550</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2313; 9585</t>
+          <t>2865; 10587</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2817; 13522</t>
+          <t>3030; 13058</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4728; 16418</t>
+          <t>4453; 16547</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3745; 15026</t>
+          <t>4447; 14811</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2317; 9716</t>
+          <t>2671; 11410</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>4534</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3809</t>
+          <t>3885</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8229</t>
+          <t>8419</t>
         </is>
       </c>
     </row>
@@ -2692,22 +2692,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>940; 8391</t>
+          <t>385; 7775</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2112; 11228</t>
+          <t>2123; 11209</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1040; 8890</t>
+          <t>1077; 9122</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1373; 11152</t>
+          <t>1170; 10692</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2717,37 +2717,37 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 8543</t>
+          <t>0; 9466</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>447; 7699</t>
+          <t>971; 8047</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1385; 7304</t>
+          <t>1333; 7174</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 8000</t>
+          <t>955; 8118</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3730; 16502</t>
+          <t>3841; 15792</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3449; 14301</t>
+          <t>3038; 13759</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3745; 14069</t>
+          <t>4060; 15374</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4367</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7977</t>
+          <t>8991</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4441</t>
+          <t>0; 4181</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2910,22 +2910,22 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5319</t>
+          <t>0; 4228</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1008; 8229</t>
+          <t>1569; 9239</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4995</t>
+          <t>0; 4278</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 7427</t>
+          <t>0; 7574</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2935,27 +2935,27 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1826; 7898</t>
+          <t>2038; 8790</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 6252</t>
+          <t>0; 5812</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 6861</t>
+          <t>0; 7141</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 5685</t>
+          <t>0; 6276</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4174; 12956</t>
+          <t>4769; 14757</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3514</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>5248</t>
         </is>
       </c>
     </row>
@@ -3113,57 +3113,57 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5438</t>
+          <t>0; 4284</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>802; 6208</t>
+          <t>0; 6085</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 5042</t>
+          <t>0; 4972</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4120</t>
+          <t>0; 4995</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2901; 10848</t>
+          <t>2919; 10827</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2031; 11013</t>
+          <t>1999; 11058</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1396; 6661</t>
+          <t>1605; 7391</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 5906</t>
+          <t>0; 4194</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2941; 12278</t>
+          <t>2900; 12230</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4695; 14285</t>
+          <t>4656; 14961</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2456; 9192</t>
+          <t>2410; 9224</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>3930</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>13274</t>
+          <t>14494</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>16396</t>
+          <t>18423</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4013</t>
+          <t>0; 4028</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3326,52 +3326,52 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1561; 7601</t>
+          <t>1567; 7578</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1291; 5907</t>
+          <t>1736; 8260</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1071; 8054</t>
+          <t>1058; 8263</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 6373</t>
+          <t>0; 5054</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1218; 11111</t>
+          <t>1271; 11080</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>9068; 17570</t>
+          <t>10108; 19922</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1171; 9948</t>
+          <t>1183; 9558</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 5534</t>
+          <t>0; 4449</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4081; 15966</t>
+          <t>4027; 15354</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>11930; 22023</t>
+          <t>13518; 24830</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17157</t>
+          <t>18847</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>39751</t>
+          <t>42255</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>56908</t>
+          <t>61101</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>10013; 24879</t>
+          <t>9685; 25623</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>14609; 33785</t>
+          <t>14526; 32864</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>17558; 36131</t>
+          <t>17590; 35275</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>10397; 29251</t>
+          <t>11255; 30416</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>6823; 20507</t>
+          <t>6149; 20042</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>13536; 31420</t>
+          <t>13971; 31828</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12618; 29936</t>
+          <t>11592; 29343</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>30958; 51066</t>
+          <t>33063; 53568</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>19210; 40138</t>
+          <t>19114; 38341</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>32422; 60169</t>
+          <t>33423; 60281</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>33563; 57282</t>
+          <t>33532; 59360</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>45885; 71479</t>
+          <t>48231; 77018</t>
         </is>
       </c>
     </row>
